--- a/contractor_forms/004_workmanship_warranty_submission--contractor_forms.xlsx
+++ b/contractor_forms/004_workmanship_warranty_submission--contractor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -776,12 +776,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'al'}</t>
+          <t>al</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'AL'}</t>
+          <t>AL</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'ak'}</t>
+          <t>ak</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'AK'}</t>
+          <t>AK</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'az'}</t>
+          <t>az</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'AZ'}</t>
+          <t>AZ</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'ar'}</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'AR'}</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'ca'}</t>
+          <t>ca</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'CA'}</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'co'}</t>
+          <t>co</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'CO'}</t>
+          <t>CO</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'ct'}</t>
+          <t>ct</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'CT'}</t>
+          <t>CT</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'de'}</t>
+          <t>de</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'DE'}</t>
+          <t>DE</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'fl'}</t>
+          <t>fl</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'FL'}</t>
+          <t>FL</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'ga'}</t>
+          <t>ga</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'GA'}</t>
+          <t>GA</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'hi'}</t>
+          <t>hi</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'HI'}</t>
+          <t>HI</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'id'}</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'ID'}</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'il'}</t>
+          <t>il</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'IL'}</t>
+          <t>IL</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'in'}</t>
+          <t>in</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'IN'}</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
@@ -1047,12 +1047,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'ia'}</t>
+          <t>ia</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'IA'}</t>
+          <t>IA</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'ks'}</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'KS'}</t>
+          <t>KS</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'ky'}</t>
+          <t>ky</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'KY'}</t>
+          <t>KY</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1098,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'la'}</t>
+          <t>la</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'LA'}</t>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -1115,12 +1115,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'ma'}</t>
+          <t>ma</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'MA'}</t>
+          <t>MA</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'md'}</t>
+          <t>md</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'MD'}</t>
+          <t>MD</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'me'}</t>
+          <t>me</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'ME'}</t>
+          <t>ME</t>
         </is>
       </c>
     </row>
@@ -1166,12 +1166,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'mi'}</t>
+          <t>mi</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'MI'}</t>
+          <t>MI</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'mn'}</t>
+          <t>mn</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'MN'}</t>
+          <t>MN</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'mo'}</t>
+          <t>mo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'MO'}</t>
+          <t>MO</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1217,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'ms'}</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'MS'}</t>
+          <t>MS</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'mt'}</t>
+          <t>mt</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'MT'}</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'nc'}</t>
+          <t>nc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'NC'}</t>
+          <t>NC</t>
         </is>
       </c>
     </row>
@@ -1268,12 +1268,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'nd'}</t>
+          <t>nd</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'ND'}</t>
+          <t>ND</t>
         </is>
       </c>
     </row>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'ne'}</t>
+          <t>ne</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'NE'}</t>
+          <t>NE</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'nh'}</t>
+          <t>nh</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'NH'}</t>
+          <t>NH</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'nj'}</t>
+          <t>nj</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'NJ'}</t>
+          <t>NJ</t>
         </is>
       </c>
     </row>
@@ -1336,12 +1336,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'nm'}</t>
+          <t>nm</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'NM'}</t>
+          <t>NM</t>
         </is>
       </c>
     </row>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'nv'}</t>
+          <t>nv</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'NV'}</t>
+          <t>NV</t>
         </is>
       </c>
     </row>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'ny'}</t>
+          <t>ny</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 'NY'}</t>
+          <t>NY</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_'oh'}</t>
+          <t>oh</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': 'OH'}</t>
+          <t>OH</t>
         </is>
       </c>
     </row>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_'ok'}</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': 'OK'}</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1421,12 +1421,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_'or'}</t>
+          <t>or</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': 'OR'}</t>
+          <t>OR</t>
         </is>
       </c>
     </row>
@@ -1438,12 +1438,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_'pa'}</t>
+          <t>pa</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': 'PA'}</t>
+          <t>PA</t>
         </is>
       </c>
     </row>
@@ -1455,12 +1455,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_'sc'}</t>
+          <t>sc</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': 'SC'}</t>
+          <t>SC</t>
         </is>
       </c>
     </row>
@@ -1472,12 +1472,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_'sd'}</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': 'SD'}</t>
+          <t>SD</t>
         </is>
       </c>
     </row>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'value':_'tn'}</t>
+          <t>tn</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'value': 'TN'}</t>
+          <t>TN</t>
         </is>
       </c>
     </row>
@@ -1506,12 +1506,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'value':_'tx'}</t>
+          <t>tx</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'value': 'TX'}</t>
+          <t>TX</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'value':_'ut'}</t>
+          <t>ut</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'value': 'UT'}</t>
+          <t>UT</t>
         </is>
       </c>
     </row>
@@ -1540,12 +1540,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'value':_'va'}</t>
+          <t>va</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'value': 'VA'}</t>
+          <t>VA</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'value':_'vt'}</t>
+          <t>vt</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'value': 'VT'}</t>
+          <t>VT</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'value':_'wa'}</t>
+          <t>wa</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'value': 'WA'}</t>
+          <t>WA</t>
         </is>
       </c>
     </row>
@@ -1591,12 +1591,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'value':_'wv'}</t>
+          <t>wv</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'value': 'WV'}</t>
+          <t>WV</t>
         </is>
       </c>
     </row>
@@ -1608,12 +1608,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'value':_'wy'}</t>
+          <t>wy</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'value': 'WY'}</t>
+          <t>WY</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'value':_'dc'}</t>
+          <t>dc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'value': 'DC'}</t>
+          <t>DC</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'value':_'pr'}</t>
+          <t>pr</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'value': 'PR'}</t>
+          <t>PR</t>
         </is>
       </c>
     </row>
@@ -1659,12 +1659,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'value':_'as'}</t>
+          <t>as</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'value': 'AS'}</t>
+          <t>AS</t>
         </is>
       </c>
     </row>
@@ -1676,12 +1676,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'value':_'gu'}</t>
+          <t>gu</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'value': 'GU'}</t>
+          <t>GU</t>
         </is>
       </c>
     </row>
@@ -1693,12 +1693,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'value':_'vi'}</t>
+          <t>vi</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'value': 'VI'}</t>
+          <t>VI</t>
         </is>
       </c>
     </row>
@@ -1710,12 +1710,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'value':_'mp'}</t>
+          <t>mp</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'value': 'MP'}</t>
+          <t>MP</t>
         </is>
       </c>
     </row>
@@ -1727,12 +1727,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'value':_'pw'}</t>
+          <t>pw</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'value': 'PW'}</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'value':_'um'}</t>
+          <t>um</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'value': 'UM'}</t>
+          <t>UM</t>
         </is>
       </c>
     </row>
@@ -1761,46 +1761,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'value':_'us'}</t>
+          <t>us</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'value': 'US'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>{'value':_'um'}</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>{'value': 'UM'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>{'value':_'mp'}</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>{'value': 'MP'}</t>
+          <t>US</t>
         </is>
       </c>
     </row>
